--- a/StructureDefinition-VunsPneumoCondition.xlsx
+++ b/StructureDefinition-VunsPneumoCondition.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$61</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2625" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2339" uniqueCount="441">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -271,8 +271,8 @@
     <t>A clinical condition, problem, diagnosis, or other event, situation, issue, or clinical concept that has risen to a level of concern.</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}con-5:Condition.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}con-4:If condition is abated, then clinicalStatus must be either inactive, resolved, or remission {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-3:Condition.clinicalStatus SHALL be present if verificationStatus is not entered-in-error and category is problem-list-item {clinicalStatus.exists() or verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code = 'entered-in-error').exists() or category.select($this='problem-list-item').empty()}</t>
+    <t>con-3:Condition.clinicalStatus SHALL be present if verificationStatus is not entered-in-error and category is problem-list-item {clinicalStatus.exists() or verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code = 'entered-in-error').exists() or category.select($this='problem-list-item').empty()}
+con-4:If condition is abated, then clinicalStatus must be either inactive, resolved, or remission {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:Condition.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -434,137 +434,131 @@
     <t>Condition.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Condition.extension:bodySite</t>
+  </si>
+  <si>
+    <t>bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {bodySite}
+</t>
+  </si>
+  <si>
+    <t>Target anatomic location or structure</t>
+  </si>
+  <si>
+    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
+  </si>
+  <si>
+    <t>Condition.extension:bodySite.id</t>
+  </si>
+  <si>
+    <t>Condition.extension.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Condition.extension:bodySite.extension</t>
+  </si>
+  <si>
+    <t>Condition.extension.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Condition.extension:bodySite.url</t>
+  </si>
+  <si>
+    <t>Condition.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/bodySite</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Condition.extension:bodySite.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.eu/fhir/base/StructureDefinition/BodyStructure-eu)
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
+  </si>
+  <si>
+    <t>Condition.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Condition.extension:bodySite</t>
-  </si>
-  <si>
-    <t>bodySite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {bodySite}
-</t>
-  </si>
-  <si>
-    <t>Target anatomic location or structure</t>
-  </si>
-  <si>
-    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Condition.extension:bodySite.id</t>
-  </si>
-  <si>
-    <t>Condition.extension.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>Condition.extension:bodySite.extension</t>
-  </si>
-  <si>
-    <t>Condition.extension.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Condition.extension:bodySite.url</t>
-  </si>
-  <si>
-    <t>Condition.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/bodySite</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Condition.extension:bodySite.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://hl7.eu/fhir/base/StructureDefinition/BodyStructure-eu)
-</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -572,6 +566,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -600,9 +597,6 @@
     <t>Event.identifier</t>
   </si>
   <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
     <t>.id</t>
   </si>
   <si>
@@ -616,7 +610,7 @@
 </t>
   </si>
   <si>
-    <t>Concept - reference to a terminology or just  text</t>
+    <t>active | recurrence | relapse | inactive | remission | resolved</t>
   </si>
   <si>
     <t>The problem status describes the condition of the problem:
@@ -625,20 +619,17 @@
 3.	Problems with the status 'Inactive' refer to problems that don't affect the patient anymore or that of which there is no evidence of existence anymore.</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+    <t>The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>The clinical status of the condition or diagnosis.</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/condition-clinical</t>
   </si>
   <si>
-    <t>ele-1
-con-3con-4con-5</t>
+    <t>con-3
+con-4con-5</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -657,20 +648,98 @@
     <t>FiveWs.status</t>
   </si>
   <si>
+    <t>Condition.clinicalStatus.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Condition.clinicalStatus.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Condition.clinicalStatus.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding {http://hl7.org/fhir/uv/ips/StructureDefinition/Coding-uv-ips}
+</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://terminology.hl7.org/CodeSystem/condition-clinical"/&gt;
+  &lt;code value="active"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>Condition.clinicalStatus.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
     <t>Condition.verificationStatus</t>
   </si>
   <si>
-    <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
-  </si>
-  <si>
-    <t>The verification status to support or decline the clinical status of the condition or diagnosis.</t>
+    <t>unconfirmed | provisional | differential | confirmed | refuted | entered-in-error</t>
+  </si>
+  <si>
+    <t>The verification status to support the clinical status of the condition.</t>
+  </si>
+  <si>
+    <t>verificationStatus is not required.  For example, when a patient has abdominal pain in the ED, there is not likely going to be a verification status.
+The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-ver-status</t>
   </si>
   <si>
-    <t>ele-1
-con-3con-5</t>
+    <t>con-3
+con-5</t>
   </si>
   <si>
     <t>&lt; 410514004 |Finding context value|</t>
@@ -695,6 +764,9 @@
     <t>Slices per type of classificaton</t>
   </si>
   <si>
+    <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
+  </si>
+  <si>
     <t>extensible</t>
   </si>
   <si>
@@ -736,9 +808,6 @@
     <t>Present on admission, Hospital acquired condition, Not applicable or unknown</t>
   </si>
   <si>
-    <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
-  </si>
-  <si>
     <t>http://terminology.ehdsi.eu/ValueSet/eHDSIConditionPOA</t>
   </si>
   <si>
@@ -760,7 +829,13 @@
     <t>Condition.severity</t>
   </si>
   <si>
+    <t>Subjective severity of condition</t>
+  </si>
+  <si>
     <t>A subjective assessment of the severity of the condition as evaluated by the clinician.</t>
+  </si>
+  <si>
+    <t>Coding of the severity with a terminology is preferred, where possible.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-severity</t>
@@ -786,6 +861,9 @@
   <si>
     <t xml:space="preserve">type
 </t>
+  </si>
+  <si>
+    <t>Identification of the condition, problem or diagnosis</t>
   </si>
   <si>
     <t>The problem code specifies the problem. Depending on the setting, different code systems can be used. The ProblemCodelist provides an overview of the possible code systems.</t>
@@ -836,232 +914,28 @@
     <t>Condition.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding {http://hl7.org/fhir/uv/ips/StructureDefinition/Coding-uv-ips}
-</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.id</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
     <t>http://si-s-serv1041.st.chulg/ig/VersUnSouffleNouveauIG/ValueSet/i2x-pneumo-diagnostic</t>
   </si>
   <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.display.id</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.display.extension</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.display.extension:translation</t>
-  </si>
-  <si>
-    <t>translation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {translation}
-</t>
-  </si>
-  <si>
-    <t>Language Translation (Localization)</t>
-  </si>
-  <si>
-    <t>Language translation from base language of resource to another language.</t>
-  </si>
-  <si>
-    <t>ST.translation</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.display.value</t>
-  </si>
-  <si>
-    <t>Primitive value for string</t>
-  </si>
-  <si>
-    <t>1048576</t>
-  </si>
-  <si>
-    <t>string.value</t>
-  </si>
-  <si>
-    <t>Condition.code.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
     <t>Condition.code.text</t>
   </si>
   <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
     <t>Condition.bodySite</t>
   </si>
   <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
+    <t>Anatomical location, if relevant</t>
+  </si>
+  <si>
+    <t>The anatomical location where this condition manifests itself.</t>
+  </si>
+  <si>
+    <t>Only used if not implicit in code found in Condition.code. If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).  May be a summary code, or a reference to a very precise definition of the location, or both.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
   </si>
   <si>
     <t>.targetBodySiteCode</t>
@@ -1087,14 +961,7 @@
     <t>Indicates the patient or group who the condition record is associated with.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Group is typically used for veterinary or public health use cases.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1277,8 +1144,8 @@
     <t>There is no explicit distinction between resolution and remission because in many cases the distinction is not clear. Age is generally used when the patient reports an age at which the Condition abated.  If there is no abatement element, it is unknown whether the condition has resolved or entered remission; applications and users should generally assume that the condition is still valid.  When abatementString exists, it implies the condition is abated.</t>
   </si>
   <si>
-    <t>ele-1
-con-4</t>
+    <t xml:space="preserve">con-4
+</t>
   </si>
   <si>
     <t>.effectiveTime.high or .inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="age at remission"].value or .inboundRelationship[typeCode=SUBJ]source[classCode=CONC, moodCode=EVN].status=completed</t>
@@ -1364,8 +1231,8 @@
     <t>Clinical stage or grade of a condition. May include formal severity assessments.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-con-1:Stage SHALL have summary or assessment {summary.exists() or assessment.exists()}</t>
+    <t>con-1:Stage SHALL have summary or assessment {summary.exists() or assessment.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="stage/grade"]</t>
@@ -1412,8 +1279,8 @@
     <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
   </si>
   <si>
-    <t>ele-1
-con-1</t>
+    <t xml:space="preserve">con-1
+</t>
   </si>
   <si>
     <t>&lt; 254291000 |Staging and scales|</t>
@@ -1465,8 +1332,8 @@
     <t>The evidence may be a simple list of coded symptoms/manifestations, or references to observations or formal assessments, or both.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-con-2:evidence SHALL have code or details {code.exists() or detail.exists()}</t>
+    <t>con-2:evidence SHALL have code or details {code.exists() or detail.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=SPRT].target[classCode=OBS, moodCode=EVN]</t>
@@ -1496,8 +1363,8 @@
     <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom</t>
   </si>
   <si>
-    <t>ele-1
-con-2</t>
+    <t xml:space="preserve">con-2
+</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1533,9 +1400,6 @@
   </si>
   <si>
     <t>Comment by the one who determined or updated the Problem.</t>
-  </si>
-  <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -1861,11 +1725,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP68"/>
+  <dimension ref="A1:AP61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="47.4765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="37.19921875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="41.5390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.19140625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="19.546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
@@ -1888,7 +1752,7 @@
     <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="82.6015625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="68.20703125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="82.47265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
@@ -2880,7 +2744,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2899,17 +2763,15 @@
         <v>19</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>139</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>19</v>
@@ -2946,19 +2808,17 @@
         <v>19</v>
       </c>
       <c r="AB9" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AC9" s="2"/>
+      <c r="AD9" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -2970,7 +2830,7 @@
         <v>19</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>19</v>
@@ -2982,7 +2842,7 @@
         <v>19</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>133</v>
+        <v>19</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>19</v>
@@ -2993,16 +2853,16 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3021,17 +2881,15 @@
         <v>19</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>19</v>
@@ -3080,7 +2938,7 @@
         <v>19</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -3089,10 +2947,10 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>19</v>
@@ -3104,7 +2962,7 @@
         <v>19</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>151</v>
+        <v>19</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>19</v>
@@ -3115,10 +2973,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3141,13 +2999,13 @@
         <v>19</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>154</v>
+        <v>92</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3198,7 +3056,7 @@
         <v>19</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3207,7 +3065,7 @@
         <v>90</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>19</v>
@@ -3222,7 +3080,7 @@
         <v>19</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>19</v>
@@ -3233,14 +3091,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3259,17 +3117,15 @@
         <v>19</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="M12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>139</v>
-      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>19</v>
@@ -3306,19 +3162,19 @@
         <v>19</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3330,7 +3186,7 @@
         <v>19</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>19</v>
@@ -3342,7 +3198,7 @@
         <v>19</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>151</v>
+        <v>19</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>19</v>
@@ -3353,10 +3209,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3382,13 +3238,13 @@
         <v>104</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3396,7 +3252,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>19</v>
@@ -3438,7 +3294,7 @@
         <v>19</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>90</v>
@@ -3473,10 +3329,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3499,13 +3355,13 @@
         <v>19</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3556,7 +3412,7 @@
         <v>19</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3565,7 +3421,7 @@
         <v>90</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>102</v>
@@ -3591,14 +3447,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3617,19 +3473,19 @@
         <v>19</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>19</v>
@@ -3666,19 +3522,19 @@
         <v>19</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>141</v>
+        <v>19</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3690,7 +3546,7 @@
         <v>19</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>19</v>
@@ -3713,10 +3569,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3739,19 +3595,19 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>19</v>
@@ -3800,7 +3656,7 @@
         <v>19</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3809,25 +3665,25 @@
         <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN16" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AL16" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>19</v>
@@ -3835,10 +3691,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3855,22 +3711,22 @@
         <v>19</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3896,13 +3752,11 @@
         <v>19</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>19</v>
@@ -3920,7 +3774,7 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3929,25 +3783,25 @@
         <v>90</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>19</v>
@@ -3955,10 +3809,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3978,20 +3832,18 @@
         <v>19</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>192</v>
+        <v>149</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>19</v>
@@ -4016,13 +3868,13 @@
         <v>19</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>195</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>206</v>
+        <v>19</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>207</v>
+        <v>19</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>19</v>
@@ -4040,7 +3892,7 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>204</v>
+        <v>151</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4049,40 +3901,40 @@
         <v>90</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>208</v>
+        <v>19</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>199</v>
+        <v>19</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>209</v>
+        <v>19</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>210</v>
+        <v>19</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>211</v>
+        <v>153</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>203</v>
+        <v>19</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>212</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>19</v>
+        <v>173</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4101,16 +3953,16 @@
         <v>19</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>191</v>
+        <v>135</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4136,29 +3988,31 @@
         <v>19</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>216</v>
+        <v>19</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>217</v>
+        <v>19</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>218</v>
+        <v>19</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AC19" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="AD19" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>213</v>
+        <v>157</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4167,25 +4021,25 @@
         <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>220</v>
+        <v>19</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>221</v>
+        <v>19</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>222</v>
+        <v>153</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>223</v>
+        <v>19</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>19</v>
@@ -4193,14 +4047,12 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>19</v>
       </c>
@@ -4209,10 +4061,10 @@
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>19</v>
@@ -4221,18 +4073,20 @@
         <v>19</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>19</v>
       </c>
@@ -4241,7 +4095,7 @@
         <v>19</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>19</v>
+        <v>212</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>19</v>
@@ -4256,13 +4110,13 @@
         <v>19</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>195</v>
+        <v>19</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>217</v>
+        <v>19</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>230</v>
+        <v>19</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>19</v>
@@ -4289,7 +4143,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>102</v>
@@ -4298,16 +4152,16 @@
         <v>19</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>220</v>
+        <v>19</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>223</v>
+        <v>19</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>19</v>
@@ -4315,14 +4169,12 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>19</v>
       </c>
@@ -4334,27 +4186,29 @@
         <v>90</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>19</v>
       </c>
@@ -4378,13 +4232,13 @@
         <v>19</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>195</v>
+        <v>19</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>217</v>
+        <v>19</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>235</v>
+        <v>19</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>19</v>
@@ -4402,16 +4256,16 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>102</v>
@@ -4420,16 +4274,16 @@
         <v>19</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>220</v>
+        <v>19</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>223</v>
+        <v>19</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>19</v>
@@ -4437,10 +4291,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4457,22 +4311,22 @@
         <v>19</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4498,13 +4352,11 @@
         <v>19</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>19</v>
@@ -4522,7 +4374,7 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4531,47 +4383,47 @@
         <v>90</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>150</v>
+        <v>229</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>19</v>
+        <v>196</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>242</v>
+        <v>200</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>243</v>
+        <v>233</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>245</v>
+        <v>19</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>19</v>
@@ -4580,23 +4432,21 @@
         <v>19</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>192</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>19</v>
       </c>
@@ -4620,71 +4470,71 @@
         <v>19</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>114</v>
+        <v>238</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>250</v>
+        <v>19</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>255</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>19</v>
       </c>
@@ -4705,15 +4555,17 @@
         <v>19</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>154</v>
+        <v>248</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>155</v>
+        <v>249</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>19</v>
@@ -4738,13 +4590,11 @@
         <v>19</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>19</v>
+        <v>251</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>19</v>
@@ -4762,34 +4612,34 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>157</v>
+        <v>234</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>19</v>
+        <v>242</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>19</v>
+        <v>243</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>151</v>
+        <v>244</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>19</v>
+        <v>245</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>19</v>
@@ -4797,21 +4647,23 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="D25" t="s" s="2">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>19</v>
@@ -4823,16 +4675,16 @@
         <v>19</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>136</v>
+        <v>248</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>137</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>160</v>
+        <v>255</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>139</v>
+        <v>237</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4858,31 +4710,29 @@
         <v>19</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>19</v>
+        <v>256</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>141</v>
+        <v>19</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>161</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4894,22 +4744,22 @@
         <v>19</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>19</v>
+        <v>242</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>19</v>
+        <v>243</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>151</v>
+        <v>244</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>19</v>
+        <v>245</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>19</v>
@@ -4917,10 +4767,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4931,32 +4781,30 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>263</v>
-      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>19</v>
       </c>
@@ -4980,13 +4828,11 @@
         <v>19</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>19</v>
+        <v>261</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>19</v>
@@ -5004,16 +4850,16 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>102</v>
@@ -5022,19 +4868,19 @@
         <v>19</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>19</v>
+        <v>262</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -5046,11 +4892,11 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>19</v>
+        <v>268</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>90</v>
@@ -5062,19 +4908,21 @@
         <v>19</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>155</v>
+        <v>269</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>156</v>
+        <v>270</v>
       </c>
       <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>19</v>
       </c>
@@ -5098,13 +4946,13 @@
         <v>19</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>19</v>
+        <v>272</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>19</v>
+        <v>273</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>19</v>
@@ -5122,7 +4970,7 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>157</v>
+        <v>267</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5134,44 +4982,44 @@
         <v>19</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>19</v>
+        <v>274</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>19</v>
+        <v>275</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>19</v>
+        <v>276</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>151</v>
+        <v>277</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>19</v>
+        <v>278</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>19</v>
+        <v>279</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>19</v>
@@ -5183,17 +5031,15 @@
         <v>19</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>136</v>
+        <v>202</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>19</v>
@@ -5230,31 +5076,31 @@
         <v>19</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>141</v>
+        <v>19</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>19</v>
@@ -5266,7 +5112,7 @@
         <v>19</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>19</v>
@@ -5277,46 +5123,44 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>19</v>
+        <v>173</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>204</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
+        <v>205</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>19</v>
       </c>
@@ -5352,31 +5196,31 @@
         <v>19</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>19</v>
+        <v>156</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>274</v>
+        <v>157</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>19</v>
@@ -5385,10 +5229,10 @@
         <v>19</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>275</v>
+        <v>19</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>276</v>
+        <v>153</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>19</v>
@@ -5399,10 +5243,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5410,33 +5254,35 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>154</v>
+        <v>207</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>278</v>
+        <v>208</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>279</v>
+        <v>209</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>19</v>
       </c>
@@ -5460,13 +5306,11 @@
         <v>19</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>19</v>
+        <v>283</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>19</v>
@@ -5484,16 +5328,16 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>281</v>
+        <v>213</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>102</v>
@@ -5505,10 +5349,10 @@
         <v>19</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>282</v>
+        <v>214</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>283</v>
+        <v>215</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>19</v>
@@ -5545,17 +5389,19 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>110</v>
+        <v>202</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>285</v>
+        <v>217</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="O31" t="s" s="2">
-        <v>287</v>
+        <v>220</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>19</v>
@@ -5580,11 +5426,13 @@
         <v>19</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="Y31" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z31" t="s" s="2">
-        <v>288</v>
+        <v>19</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>19</v>
@@ -5602,7 +5450,7 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>289</v>
+        <v>221</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5623,10 +5471,10 @@
         <v>19</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>290</v>
+        <v>222</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>291</v>
+        <v>223</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>19</v>
@@ -5637,10 +5485,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5651,10 +5499,10 @@
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>19</v>
@@ -5663,20 +5511,18 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>19</v>
       </c>
@@ -5700,13 +5546,11 @@
         <v>19</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>19</v>
+        <v>289</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>19</v>
@@ -5724,13 +5568,13 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>19</v>
@@ -5742,35 +5586,35 @@
         <v>19</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>19</v>
+        <v>290</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>298</v>
+        <v>19</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>19</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>19</v>
+        <v>294</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>90</v>
@@ -5782,19 +5626,21 @@
         <v>19</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>154</v>
+        <v>295</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>155</v>
+        <v>296</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>156</v>
+        <v>297</v>
       </c>
       <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>19</v>
       </c>
@@ -5842,10 +5688,10 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>157</v>
+        <v>293</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>90</v>
@@ -5854,22 +5700,22 @@
         <v>19</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>19</v>
+        <v>299</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>19</v>
+        <v>300</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>151</v>
+        <v>301</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>19</v>
+        <v>302</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>19</v>
@@ -5877,21 +5723,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>19</v>
@@ -5903,17 +5749,15 @@
         <v>19</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>136</v>
+        <v>202</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>19</v>
@@ -5950,31 +5794,31 @@
         <v>19</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>141</v>
+        <v>19</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>19</v>
@@ -5986,7 +5830,7 @@
         <v>19</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>19</v>
@@ -5997,16 +5841,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6025,16 +5867,16 @@
         <v>19</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>304</v>
+        <v>135</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>305</v>
+        <v>204</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>306</v>
+        <v>205</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6072,19 +5914,19 @@
         <v>19</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>19</v>
+        <v>156</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6093,10 +5935,10 @@
         <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>19</v>
@@ -6108,7 +5950,7 @@
         <v>19</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>307</v>
+        <v>153</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>19</v>
@@ -6119,10 +5961,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6130,7 +5972,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>90</v>
@@ -6142,18 +5984,20 @@
         <v>19</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>154</v>
+        <v>202</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>19</v>
@@ -6175,7 +6019,7 @@
         <v>19</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>310</v>
+        <v>19</v>
       </c>
       <c r="X36" t="s" s="2">
         <v>19</v>
@@ -6202,7 +6046,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6211,10 +6055,10 @@
         <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>19</v>
+        <v>310</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>19</v>
@@ -6226,7 +6070,7 @@
         <v>19</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>19</v>
+        <v>133</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>19</v>
@@ -6237,10 +6081,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6263,20 +6107,18 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>317</v>
-      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>19</v>
       </c>
@@ -6300,13 +6142,13 @@
         <v>19</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>19</v>
+        <v>238</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>19</v>
+        <v>315</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>19</v>
+        <v>316</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>19</v>
@@ -6324,7 +6166,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6345,10 +6187,10 @@
         <v>19</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>320</v>
+        <v>133</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>19</v>
@@ -6359,10 +6201,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6376,7 +6218,7 @@
         <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>19</v>
@@ -6385,20 +6227,18 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>19</v>
       </c>
@@ -6446,7 +6286,7 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6467,10 +6307,10 @@
         <v>19</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>327</v>
+        <v>19</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>19</v>
@@ -6481,10 +6321,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6495,7 +6335,7 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>19</v>
@@ -6507,16 +6347,16 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>192</v>
+        <v>325</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>205</v>
+        <v>326</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>194</v>
+        <v>327</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6542,13 +6382,13 @@
         <v>19</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>330</v>
+        <v>19</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>331</v>
+        <v>19</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>19</v>
@@ -6566,16 +6406,16 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>102</v>
@@ -6584,35 +6424,35 @@
         <v>19</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>333</v>
+        <v>19</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>334</v>
+        <v>133</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>335</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>337</v>
+        <v>19</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>90</v>
@@ -6627,20 +6467,18 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>19</v>
       </c>
@@ -6688,34 +6526,34 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>343</v>
+        <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>19</v>
@@ -6723,10 +6561,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6746,18 +6584,20 @@
         <v>19</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>154</v>
+        <v>339</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>155</v>
+        <v>340</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>19</v>
@@ -6794,19 +6634,17 @@
         <v>19</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>157</v>
+        <v>338</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6818,22 +6656,22 @@
         <v>19</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>19</v>
+        <v>344</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>19</v>
+        <v>345</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>151</v>
+        <v>346</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>19</v>
+        <v>347</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>19</v>
@@ -6841,21 +6679,23 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="C42" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="B42" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>19</v>
@@ -6864,19 +6704,19 @@
         <v>19</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>136</v>
+        <v>350</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>137</v>
+        <v>340</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>160</v>
+        <v>351</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>139</v>
+        <v>342</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6914,46 +6754,46 @@
         <v>19</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>141</v>
+        <v>19</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>161</v>
+        <v>338</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>19</v>
+        <v>344</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>19</v>
+        <v>345</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>151</v>
+        <v>346</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>19</v>
+        <v>347</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>19</v>
@@ -6961,10 +6801,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6972,7 +6812,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>90</v>
@@ -6984,19 +6824,19 @@
         <v>19</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>154</v>
+        <v>339</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7034,19 +6874,17 @@
         <v>19</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7055,7 +6893,7 @@
         <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>102</v>
@@ -7070,10 +6908,10 @@
         <v>19</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>133</v>
+        <v>357</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>19</v>
+        <v>358</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>19</v>
@@ -7081,12 +6919,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>19</v>
       </c>
@@ -7104,19 +6944,19 @@
         <v>19</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>104</v>
+        <v>350</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7142,13 +6982,13 @@
         <v>19</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>216</v>
+        <v>19</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>19</v>
@@ -7166,7 +7006,7 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7175,7 +7015,7 @@
         <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>19</v>
+        <v>356</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>102</v>
@@ -7190,10 +7030,10 @@
         <v>19</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>133</v>
+        <v>357</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>19</v>
+        <v>358</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>19</v>
@@ -7201,10 +7041,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7227,17 +7067,15 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>181</v>
+        <v>350</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M45" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>366</v>
-      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>19</v>
@@ -7286,7 +7124,7 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7295,7 +7133,7 @@
         <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>102</v>
@@ -7307,13 +7145,13 @@
         <v>19</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>187</v>
+        <v>365</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>19</v>
+        <v>367</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>19</v>
@@ -7321,10 +7159,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7347,7 +7185,7 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>154</v>
+        <v>369</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>370</v>
@@ -7355,9 +7193,7 @@
       <c r="M46" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="N46" t="s" s="2">
-        <v>372</v>
-      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>19</v>
@@ -7406,7 +7242,7 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7430,10 +7266,10 @@
         <v>19</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>133</v>
+        <v>372</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>19</v>
+        <v>373</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>19</v>
@@ -7467,17 +7303,15 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M47" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>378</v>
-      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>19</v>
@@ -7535,25 +7369,25 @@
         <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>343</v>
+        <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>19</v>
@@ -7561,10 +7395,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7575,7 +7409,7 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>19</v>
@@ -7584,20 +7418,18 @@
         <v>19</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>19</v>
@@ -7634,44 +7466,46 @@
         <v>19</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AC48" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD48" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>102</v>
+        <v>384</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>389</v>
+        <v>19</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>390</v>
+        <v>19</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>392</v>
+        <v>19</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>19</v>
@@ -7679,14 +7513,12 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>19</v>
       </c>
@@ -7704,20 +7536,18 @@
         <v>19</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>395</v>
+        <v>202</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>385</v>
+        <v>149</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -7766,7 +7596,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>383</v>
+        <v>151</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7775,25 +7605,25 @@
         <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>389</v>
+        <v>19</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>390</v>
+        <v>19</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>391</v>
+        <v>153</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>392</v>
+        <v>19</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>19</v>
@@ -7801,21 +7631,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>19</v>
+        <v>173</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>19</v>
@@ -7827,16 +7657,16 @@
         <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>384</v>
+        <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>398</v>
+        <v>204</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>399</v>
+        <v>205</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>400</v>
+        <v>176</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7874,29 +7704,31 @@
         <v>19</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AC50" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD50" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>397</v>
+        <v>157</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>401</v>
+        <v>19</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>19</v>
@@ -7908,10 +7740,10 @@
         <v>19</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>402</v>
+        <v>153</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>403</v>
+        <v>19</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>19</v>
@@ -7919,46 +7751,46 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>19</v>
+        <v>389</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>395</v>
+        <v>135</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>19</v>
       </c>
@@ -8006,19 +7838,19 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>401</v>
+        <v>19</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>19</v>
@@ -8030,10 +7862,10 @@
         <v>19</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>402</v>
+        <v>133</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>403</v>
+        <v>19</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>19</v>
@@ -8041,10 +7873,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8064,16 +7896,16 @@
         <v>19</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8100,13 +7932,13 @@
         <v>19</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>19</v>
+        <v>396</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>19</v>
+        <v>397</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>19</v>
+        <v>398</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>19</v>
@@ -8124,7 +7956,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8133,7 +7965,7 @@
         <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>19</v>
+        <v>399</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>102</v>
@@ -8142,16 +7974,16 @@
         <v>19</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>19</v>
+        <v>400</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>410</v>
+        <v>198</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>411</v>
+        <v>277</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>412</v>
+        <v>19</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>19</v>
@@ -8159,10 +7991,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8173,7 +8005,7 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>19</v>
@@ -8182,20 +8014,18 @@
         <v>19</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>19</v>
@@ -8244,19 +8074,19 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>150</v>
+        <v>399</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>343</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>19</v>
@@ -8268,10 +8098,10 @@
         <v>19</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>418</v>
+        <v>19</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>19</v>
@@ -8279,10 +8109,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8302,20 +8132,18 @@
         <v>19</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>414</v>
+        <v>248</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>19</v>
@@ -8340,13 +8168,13 @@
         <v>19</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>19</v>
+        <v>396</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>19</v>
+        <v>409</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>19</v>
+        <v>410</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>19</v>
@@ -8364,7 +8192,7 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8373,10 +8201,10 @@
         <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>343</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>19</v>
@@ -8385,13 +8213,13 @@
         <v>19</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>422</v>
+        <v>19</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>424</v>
+        <v>19</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>19</v>
@@ -8399,10 +8227,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8425,15 +8253,17 @@
         <v>19</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>426</v>
+        <v>381</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>19</v>
@@ -8482,7 +8312,7 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8491,10 +8321,10 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>19</v>
@@ -8506,7 +8336,7 @@
         <v>19</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>19</v>
@@ -8517,10 +8347,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8543,13 +8373,13 @@
         <v>19</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>154</v>
+        <v>202</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8600,7 +8430,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8624,7 +8454,7 @@
         <v>19</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>19</v>
@@ -8635,14 +8465,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8661,16 +8491,16 @@
         <v>19</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8708,19 +8538,19 @@
         <v>19</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>141</v>
+        <v>19</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8732,7 +8562,7 @@
         <v>19</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>19</v>
@@ -8744,7 +8574,7 @@
         <v>19</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>19</v>
@@ -8755,14 +8585,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>434</v>
+        <v>389</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8781,19 +8611,19 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>435</v>
+        <v>390</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>436</v>
+        <v>391</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>19</v>
@@ -8842,7 +8672,7 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>437</v>
+        <v>392</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8854,7 +8684,7 @@
         <v>19</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>19</v>
@@ -8877,10 +8707,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8891,7 +8721,7 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>19</v>
@@ -8900,20 +8730,18 @@
         <v>19</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>439</v>
+        <v>422</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>19</v>
@@ -8938,13 +8766,13 @@
         <v>19</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>441</v>
+        <v>396</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>19</v>
@@ -8962,34 +8790,34 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>19</v>
+        <v>427</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>445</v>
+        <v>242</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>201</v>
+        <v>19</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>253</v>
+        <v>428</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>19</v>
+        <v>429</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>19</v>
@@ -8997,10 +8825,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9020,20 +8848,18 @@
         <v>19</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>19</v>
@@ -9082,7 +8908,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9091,10 +8917,10 @@
         <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>343</v>
+        <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>19</v>
@@ -9106,10 +8932,10 @@
         <v>19</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>450</v>
+        <v>405</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>19</v>
+        <v>429</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>19</v>
@@ -9117,10 +8943,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9131,7 +8957,7 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>19</v>
@@ -9143,17 +8969,15 @@
         <v>19</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>226</v>
+        <v>435</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>19</v>
@@ -9178,13 +9002,13 @@
         <v>19</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>454</v>
+        <v>19</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>455</v>
+        <v>19</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>19</v>
@@ -9202,881 +9026,41 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>19</v>
+        <v>438</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>333</v>
+        <v>439</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AP68" t="s" s="2">
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP68">
+  <autoFilter ref="A1:AP61">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10086,7 +9070,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI67">
+  <conditionalFormatting sqref="A2:AI60">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-VunsPneumoCondition.xlsx
+++ b/StructureDefinition-VunsPneumoCondition.xlsx
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profile pour un diagnostic pneumologique</t>
+    <t>Profile for primary diagnosis</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/StructureDefinition-VunsPneumoCondition.xlsx
+++ b/StructureDefinition-VunsPneumoCondition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-VunsPneumoCondition.xlsx
+++ b/StructureDefinition-VunsPneumoCondition.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$73</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2339" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2793" uniqueCount="499">
   <si>
     <t>Property</t>
   </si>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profile for primary diagnosis</t>
+    <t>Profile for comorbidities and diagnoses in the scope of chronic respiratory disease remote monitoring</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>RM@H IG (C) 2025-2025 University Hospital of Liege, GSI Department, Belgium. This implementation guide is free software: you can redistribute it and/or modify it under the terms of the GNU General Public License as published by the Free Software Foundation, either version 3 of the License, or (at your option) any later version. This program is distributed in the hope that it will be useful, but WITHOUT ANY WARRANTY; without even the implied warranty of MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE. See the GNU General Public License for more details. You should have received a copy of the GNU General Public License along with this program. If not, see &lt;http://www.gnu.org/licenses/&gt;.</t>
+    <t>VUNS IG (C) 2025-2025 University Hospital of Liege, GSI Department, Belgium. This implementation guide is free software: you can redistribute it and/or modify it under the terms of the GNU General Public License as published by the Free Software Foundation, either version 3 of the License, or (at your option) any later version. This program is distributed in the hope that it will be useful, but WITHOUT ANY WARRANTY; without even the implied warranty of MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE. See the GNU General Public License for more details. You should have received a copy of the GNU General Public License along with this program. If not, see &lt;http://www.gnu.org/licenses/&gt;.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -824,6 +824,15 @@
   </si>
   <si>
     <t>http://terminology.ehdsi.eu/ValueSet/eHDSITreatmentClass</t>
+  </si>
+  <si>
+    <t>Condition.category:otherDiagnosis</t>
+  </si>
+  <si>
+    <t>otherDiagnosis</t>
+  </si>
+  <si>
+    <t>http://si-s-serv1041.st.chulg/ig/VersUnSouffleNouveauIG/ValueSet/i2x-pneumo-other-diagnosis-category</t>
   </si>
   <si>
     <t>Condition.severity</t>
@@ -914,7 +923,174 @@
     <t>Condition.code.coding</t>
   </si>
   <si>
-    <t>http://si-s-serv1041.st.chulg/ig/VersUnSouffleNouveauIG/ValueSet/i2x-pneumo-diagnostic</t>
+    <t>Condition.code.coding.id</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.display.id</t>
+  </si>
+  <si>
+    <t>xml:id (or equivalent in JSON)</t>
+  </si>
+  <si>
+    <t>unique id for the element within a resource (for internal references)</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.display.extension</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.display.extension:translation</t>
+  </si>
+  <si>
+    <t>translation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {translation}
+</t>
+  </si>
+  <si>
+    <t>Language Translation (Localization)</t>
+  </si>
+  <si>
+    <t>Language translation from base language of resource to another language.</t>
+  </si>
+  <si>
+    <t>ST.translation</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.display.value</t>
+  </si>
+  <si>
+    <t>Primitive value for string</t>
+  </si>
+  <si>
+    <t>The actual value</t>
+  </si>
+  <si>
+    <t>1048576</t>
+  </si>
+  <si>
+    <t>string.value</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
   </si>
   <si>
     <t>Condition.code.text</t>
@@ -1725,11 +1901,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP61"/>
+  <dimension ref="A1:AP73"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41.5390625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="35.19140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.4765625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="37.19921875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="19.546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
@@ -1753,7 +1929,7 @@
     <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="68.20703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="82.47265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="95.69921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="40.0390625" customWidth="true" bestFit="true"/>
@@ -4420,7 +4596,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>80</v>
@@ -4770,15 +4946,17 @@
         <v>257</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>90</v>
@@ -4796,13 +4974,13 @@
         <v>189</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4828,11 +5006,11 @@
         <v>19</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>114</v>
+        <v>193</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>19</v>
@@ -4850,13 +5028,13 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>19</v>
@@ -4868,35 +5046,35 @@
         <v>19</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>266</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>268</v>
+        <v>19</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>90</v>
@@ -4908,21 +5086,21 @@
         <v>19</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K27" t="s" s="2">
         <v>189</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>19</v>
       </c>
@@ -4948,11 +5126,9 @@
       <c r="X27" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="Y27" t="s" s="2">
-        <v>272</v>
-      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>19</v>
@@ -4970,7 +5146,7 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4985,38 +5161,38 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>274</v>
+        <v>19</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>279</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>19</v>
+        <v>271</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>90</v>
@@ -5028,19 +5204,21 @@
         <v>19</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>149</v>
+        <v>272</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>150</v>
+        <v>273</v>
       </c>
       <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+      <c r="O28" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>19</v>
       </c>
@@ -5064,13 +5242,13 @@
         <v>19</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>19</v>
+        <v>275</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>19</v>
+        <v>276</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>19</v>
@@ -5088,7 +5266,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>151</v>
+        <v>270</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5100,44 +5278,44 @@
         <v>19</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>19</v>
+        <v>277</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>19</v>
+        <v>278</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>19</v>
+        <v>279</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>153</v>
+        <v>280</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>19</v>
+        <v>281</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>19</v>
+        <v>282</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>173</v>
+        <v>19</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>19</v>
@@ -5149,17 +5327,15 @@
         <v>19</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>135</v>
+        <v>202</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>204</v>
+        <v>149</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>19</v>
@@ -5196,31 +5372,31 @@
         <v>19</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>141</v>
+        <v>19</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>19</v>
@@ -5243,24 +5419,24 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>19</v>
+        <v>173</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>19</v>
@@ -5269,20 +5445,18 @@
         <v>19</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>207</v>
+        <v>135</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>19</v>
       </c>
@@ -5306,29 +5480,31 @@
         <v>19</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>283</v>
+        <v>19</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>19</v>
+        <v>156</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>213</v>
+        <v>157</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5337,10 +5513,10 @@
         <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>152</v>
+        <v>19</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>19</v>
@@ -5349,10 +5525,10 @@
         <v>19</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>214</v>
+        <v>19</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>215</v>
+        <v>153</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>19</v>
@@ -5363,10 +5539,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5374,7 +5550,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>90</v>
@@ -5386,22 +5562,22 @@
         <v>19</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>19</v>
@@ -5450,16 +5626,16 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>102</v>
@@ -5471,10 +5647,10 @@
         <v>19</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>19</v>
@@ -5485,10 +5661,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5499,7 +5675,7 @@
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>19</v>
@@ -5508,20 +5684,18 @@
         <v>19</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>286</v>
+        <v>149</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>19</v>
@@ -5546,11 +5720,13 @@
         <v>19</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z32" t="s" s="2">
-        <v>289</v>
+        <v>19</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>19</v>
@@ -5568,56 +5744,56 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>285</v>
+        <v>151</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>290</v>
+        <v>19</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>291</v>
+        <v>153</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>292</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>294</v>
+        <v>173</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>19</v>
@@ -5626,21 +5802,21 @@
         <v>19</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>295</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>296</v>
+        <v>204</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>19</v>
       </c>
@@ -5676,46 +5852,46 @@
         <v>19</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>19</v>
+        <v>156</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>157</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>299</v>
+        <v>19</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>300</v>
+        <v>19</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>301</v>
+        <v>153</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>302</v>
+        <v>19</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>19</v>
@@ -5723,10 +5899,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5740,25 +5916,29 @@
         <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>202</v>
+        <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>149</v>
+        <v>289</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>19</v>
       </c>
@@ -5767,7 +5947,7 @@
         <v>19</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>19</v>
+        <v>293</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>19</v>
@@ -5806,7 +5986,7 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>151</v>
+        <v>294</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5818,7 +5998,7 @@
         <v>19</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>19</v>
@@ -5827,10 +6007,10 @@
         <v>19</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>19</v>
+        <v>295</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>153</v>
+        <v>296</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>19</v>
@@ -5841,21 +6021,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>173</v>
+        <v>19</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>19</v>
@@ -5864,19 +6044,19 @@
         <v>19</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>135</v>
+        <v>202</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>204</v>
+        <v>298</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>205</v>
+        <v>299</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>176</v>
+        <v>300</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5914,31 +6094,31 @@
         <v>19</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>156</v>
+        <v>19</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>157</v>
+        <v>301</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>19</v>
@@ -5947,10 +6127,10 @@
         <v>19</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>19</v>
+        <v>302</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>153</v>
+        <v>303</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>19</v>
@@ -5961,10 +6141,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5972,13 +6152,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>19</v>
@@ -5987,18 +6167,18 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>202</v>
+        <v>110</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="N36" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>19</v>
       </c>
@@ -6046,7 +6226,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6055,7 +6235,7 @@
         <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>310</v>
+        <v>19</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>102</v>
@@ -6067,10 +6247,10 @@
         <v>19</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>19</v>
+        <v>309</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>133</v>
+        <v>310</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>19</v>
@@ -6098,7 +6278,7 @@
         <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>19</v>
@@ -6107,7 +6287,7 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>104</v>
+        <v>202</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>312</v>
@@ -6115,10 +6295,10 @@
       <c r="M37" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="N37" s="2"/>
+      <c r="O37" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>19</v>
       </c>
@@ -6142,31 +6322,31 @@
         <v>19</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>238</v>
+        <v>19</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6187,10 +6367,10 @@
         <v>19</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>19</v>
+        <v>316</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>133</v>
+        <v>317</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>19</v>
@@ -6224,10 +6404,10 @@
         <v>19</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>319</v>
@@ -6235,9 +6415,7 @@
       <c r="M38" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="N38" t="s" s="2">
-        <v>321</v>
-      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>19</v>
@@ -6286,7 +6464,7 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>322</v>
+        <v>151</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6298,7 +6476,7 @@
         <v>19</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>19</v>
@@ -6310,7 +6488,7 @@
         <v>19</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>323</v>
+        <v>19</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>19</v>
@@ -6321,10 +6499,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6335,7 +6513,7 @@
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>19</v>
@@ -6344,20 +6522,18 @@
         <v>19</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>202</v>
+        <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>325</v>
+        <v>136</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>19</v>
@@ -6394,31 +6570,29 @@
         <v>19</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC39" s="2"/>
       <c r="AD39" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>328</v>
+        <v>157</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>19</v>
@@ -6430,7 +6604,7 @@
         <v>19</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>133</v>
+        <v>19</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>19</v>
@@ -6441,12 +6615,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="D40" t="s" s="2">
         <v>19</v>
       </c>
@@ -6455,7 +6631,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>19</v>
@@ -6464,20 +6640,18 @@
         <v>19</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>19</v>
@@ -6526,34 +6700,34 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>329</v>
+        <v>157</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>334</v>
+        <v>19</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>335</v>
+        <v>19</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>337</v>
+        <v>19</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>19</v>
@@ -6561,10 +6735,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6584,20 +6758,18 @@
         <v>19</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>339</v>
+        <v>202</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>19</v>
@@ -6619,7 +6791,7 @@
         <v>19</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>19</v>
+        <v>331</v>
       </c>
       <c r="X41" t="s" s="2">
         <v>19</v>
@@ -6634,17 +6806,19 @@
         <v>19</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6656,22 +6830,22 @@
         <v>19</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>344</v>
+        <v>19</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>345</v>
+        <v>19</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>346</v>
+        <v>19</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>347</v>
+        <v>19</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>19</v>
@@ -6679,14 +6853,12 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>349</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>19</v>
       </c>
@@ -6707,18 +6879,20 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>19</v>
       </c>
@@ -6766,7 +6940,7 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6781,19 +6955,19 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>344</v>
+        <v>19</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>347</v>
+        <v>19</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>19</v>
@@ -6801,10 +6975,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6818,27 +6992,29 @@
         <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>339</v>
+        <v>202</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>353</v>
+        <v>217</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>354</v>
+        <v>218</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>19</v>
       </c>
@@ -6874,17 +7050,19 @@
         <v>19</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AC43" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD43" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>352</v>
+        <v>221</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6893,7 +7071,7 @@
         <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>356</v>
+        <v>19</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>102</v>
@@ -6905,13 +7083,13 @@
         <v>19</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>19</v>
+        <v>222</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>357</v>
+        <v>223</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>358</v>
+        <v>19</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>19</v>
@@ -6919,14 +7097,12 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>19</v>
       </c>
@@ -6935,7 +7111,7 @@
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>19</v>
@@ -6944,19 +7120,19 @@
         <v>19</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>350</v>
+        <v>189</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6982,13 +7158,11 @@
         <v>19</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>19</v>
+        <v>347</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>19</v>
@@ -7006,16 +7180,16 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>356</v>
+        <v>19</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>102</v>
@@ -7024,35 +7198,35 @@
         <v>19</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>19</v>
+        <v>348</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>358</v>
+        <v>19</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>19</v>
+        <v>350</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>19</v>
+        <v>352</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>90</v>
@@ -7067,16 +7241,18 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>19</v>
       </c>
@@ -7124,10 +7300,10 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>90</v>
@@ -7139,19 +7315,19 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>19</v>
+        <v>357</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>19</v>
@@ -7159,10 +7335,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7182,16 +7358,16 @@
         <v>19</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>369</v>
+        <v>202</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>370</v>
+        <v>149</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>371</v>
+        <v>150</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7242,7 +7418,7 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>368</v>
+        <v>151</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7254,7 +7430,7 @@
         <v>19</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>19</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>19</v>
@@ -7266,10 +7442,10 @@
         <v>19</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>372</v>
+        <v>153</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>373</v>
+        <v>19</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>19</v>
@@ -7277,21 +7453,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>19</v>
+        <v>173</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>19</v>
@@ -7300,18 +7476,20 @@
         <v>19</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>369</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>375</v>
+        <v>204</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>19</v>
@@ -7348,31 +7526,31 @@
         <v>19</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>19</v>
+        <v>156</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>374</v>
+        <v>157</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>19</v>
@@ -7381,13 +7559,13 @@
         <v>19</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>377</v>
+        <v>19</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>378</v>
+        <v>153</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>379</v>
+        <v>19</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>19</v>
@@ -7395,10 +7573,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7406,10 +7584,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>19</v>
@@ -7418,18 +7596,20 @@
         <v>19</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>381</v>
+        <v>202</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>366</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>19</v>
@@ -7478,19 +7658,19 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>19</v>
+        <v>368</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>384</v>
+        <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>19</v>
@@ -7502,7 +7682,7 @@
         <v>19</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>385</v>
+        <v>133</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>19</v>
@@ -7513,10 +7693,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7536,18 +7716,20 @@
         <v>19</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>202</v>
+        <v>104</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>149</v>
+        <v>370</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -7572,13 +7754,13 @@
         <v>19</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>19</v>
+        <v>238</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>19</v>
+        <v>373</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>19</v>
+        <v>374</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>19</v>
@@ -7596,7 +7778,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>151</v>
+        <v>375</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7608,7 +7790,7 @@
         <v>19</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>19</v>
@@ -7620,7 +7802,7 @@
         <v>19</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>19</v>
@@ -7631,21 +7813,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>173</v>
+        <v>19</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>19</v>
@@ -7654,19 +7836,19 @@
         <v>19</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>204</v>
+        <v>377</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>205</v>
+        <v>378</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>176</v>
+        <v>379</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7716,19 +7898,19 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>157</v>
+        <v>380</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>19</v>
@@ -7740,7 +7922,7 @@
         <v>19</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>153</v>
+        <v>381</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>19</v>
@@ -7751,46 +7933,44 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>389</v>
+        <v>19</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>135</v>
+        <v>202</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>19</v>
       </c>
@@ -7838,19 +8018,19 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>19</v>
@@ -7873,10 +8053,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7896,18 +8076,20 @@
         <v>19</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>248</v>
+        <v>388</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>19</v>
@@ -7932,13 +8114,13 @@
         <v>19</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>396</v>
+        <v>19</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>397</v>
+        <v>19</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>398</v>
+        <v>19</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>19</v>
@@ -7956,7 +8138,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7965,25 +8147,25 @@
         <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>399</v>
+        <v>19</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>19</v>
+        <v>392</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>400</v>
+        <v>19</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>198</v>
+        <v>393</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>277</v>
+        <v>394</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>19</v>
+        <v>395</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>19</v>
@@ -7991,10 +8173,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8005,7 +8187,7 @@
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>19</v>
@@ -8014,18 +8196,20 @@
         <v>19</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>19</v>
@@ -8062,46 +8246,44 @@
         <v>19</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>399</v>
+        <v>19</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>19</v>
+        <v>402</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>19</v>
+        <v>403</v>
       </c>
       <c r="AN53" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>19</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>19</v>
@@ -8112,9 +8294,11 @@
         <v>406</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="C54" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="D54" t="s" s="2">
         <v>19</v>
       </c>
@@ -8132,18 +8316,20 @@
         <v>19</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>248</v>
+        <v>408</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>19</v>
@@ -8168,31 +8354,31 @@
         <v>19</v>
       </c>
       <c r="X54" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8207,19 +8393,19 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>19</v>
+        <v>402</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>19</v>
+        <v>403</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>19</v>
+        <v>405</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>19</v>
@@ -8227,10 +8413,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8241,7 +8427,7 @@
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>19</v>
@@ -8253,16 +8439,16 @@
         <v>19</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8300,46 +8486,44 @@
         <v>19</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>19</v>
+        <v>414</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>19</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>19</v>
@@ -8347,12 +8531,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C56" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="B56" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>19</v>
       </c>
@@ -8373,15 +8559,17 @@
         <v>19</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>202</v>
+        <v>408</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>149</v>
+        <v>411</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>19</v>
@@ -8430,7 +8618,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>151</v>
+        <v>410</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8439,10 +8627,10 @@
         <v>90</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>19</v>
+        <v>414</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>19</v>
@@ -8454,10 +8642,10 @@
         <v>19</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>153</v>
+        <v>415</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>19</v>
+        <v>416</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>19</v>
@@ -8465,21 +8653,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>173</v>
+        <v>19</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>19</v>
@@ -8488,20 +8676,18 @@
         <v>19</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>135</v>
+        <v>408</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>204</v>
+        <v>421</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>19</v>
@@ -8550,19 +8736,19 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>157</v>
+        <v>420</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>19</v>
@@ -8571,13 +8757,13 @@
         <v>19</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>19</v>
+        <v>423</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>153</v>
+        <v>424</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>19</v>
+        <v>425</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>19</v>
@@ -8585,46 +8771,42 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>389</v>
+        <v>19</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>135</v>
+        <v>427</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>390</v>
+        <v>428</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>19</v>
       </c>
@@ -8672,19 +8854,19 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>19</v>
@@ -8696,10 +8878,10 @@
         <v>19</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>133</v>
+        <v>430</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>19</v>
+        <v>431</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>19</v>
@@ -8707,10 +8889,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8721,7 +8903,7 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>19</v>
@@ -8733,13 +8915,13 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>248</v>
+        <v>427</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8766,13 +8948,13 @@
         <v>19</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>396</v>
+        <v>19</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>424</v>
+        <v>19</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>425</v>
+        <v>19</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>19</v>
@@ -8790,34 +8972,34 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>426</v>
+        <v>19</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>427</v>
+        <v>19</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>242</v>
+        <v>19</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>19</v>
+        <v>435</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>19</v>
@@ -8825,10 +9007,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8848,16 +9030,16 @@
         <v>19</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8908,7 +9090,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8917,10 +9099,10 @@
         <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>426</v>
+        <v>19</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>102</v>
+        <v>442</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>19</v>
@@ -8932,10 +9114,10 @@
         <v>19</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>405</v>
+        <v>443</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>429</v>
+        <v>19</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>19</v>
@@ -8943,10 +9125,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8957,7 +9139,7 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>19</v>
@@ -8969,13 +9151,13 @@
         <v>19</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>435</v>
+        <v>202</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>436</v>
+        <v>149</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>437</v>
+        <v>150</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9026,41 +9208,1471 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>434</v>
+        <v>151</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G62" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AI61" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
+      <c r="H62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK61" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AK64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K67" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AN61" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AP61" t="s" s="2">
+      <c r="L67" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP61">
+  <autoFilter ref="A1:AP73">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9070,7 +10682,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI60">
+  <conditionalFormatting sqref="A2:AI72">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
